--- a/직업표.xlsx
+++ b/직업표.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\python\merge-rpg\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DCFE1302-098E-402B-9EBC-BEE81BD4C122}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABDC4299-F34C-43D7-84BD-FCF1E01F5594}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8145" yWindow="915" windowWidth="18225" windowHeight="14505" xr2:uid="{AD7062BD-688C-4170-8437-0F5700B0E66B}"/>
+    <workbookView xWindow="-12060" yWindow="1500" windowWidth="19065" windowHeight="14505" xr2:uid="{AD7062BD-688C-4170-8437-0F5700B0E66B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -42,10 +42,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>도적</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>소드맨</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -298,10 +294,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>베놈서</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>템페스트 랜서</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -310,10 +302,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>플레처</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>스타시어</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -363,6 +351,18 @@
   </si>
   <si>
     <t>5차</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>로그</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>샤프슈터</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>베놈맨서</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -434,9 +434,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -445,6 +442,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -791,355 +791,355 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="4"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="4"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="4"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="4"/>
+      <c r="B6" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="4"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="4"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="4"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="4"/>
+      <c r="B10" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="4"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="4"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="4"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="4"/>
+      <c r="B14" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="4"/>
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="4"/>
+      <c r="B16" s="3"/>
+      <c r="C16" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="4"/>
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="4"/>
+      <c r="B18" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="F1" s="2" t="s">
+      <c r="D18" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="4"/>
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="4"/>
+      <c r="B20" s="3"/>
+      <c r="C20" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="4"/>
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="2" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="1"/>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="1"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="1"/>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="1"/>
-      <c r="B6" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="1"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="1"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="1"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="1"/>
-      <c r="B10" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="1"/>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="1"/>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="1"/>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="1"/>
-      <c r="B14" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="1"/>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="1"/>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="E16" s="3" t="s">
+      <c r="E21" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="F16" s="3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="1"/>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="E17" s="3" t="s">
+      <c r="F21" s="2" t="s">
         <v>71</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="1"/>
-      <c r="B18" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="1"/>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="1"/>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="1"/>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>74</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="C2:C3"/>
     <mergeCell ref="A2:A21"/>
     <mergeCell ref="B2:B5"/>
     <mergeCell ref="B6:B9"/>
     <mergeCell ref="B10:B13"/>
     <mergeCell ref="B14:B17"/>
     <mergeCell ref="B18:B21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="C18:C19"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
